--- a/diseases/d040/2000-2004.xlsx
+++ b/diseases/d040/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18637,7 +18637,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21919,7 +21919,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -23238,7 +23238,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24557,7 +24557,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -25876,7 +25876,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29833,7 +29833,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -31152,7 +31152,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32471,7 +32471,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -33790,7 +33790,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35109,7 +35109,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -36428,7 +36428,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -39792,7 +39792,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -41276,7 +41276,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -42760,7 +42760,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44244,7 +44244,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45728,7 +45728,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -47212,7 +47212,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -48696,7 +48696,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -50180,7 +50180,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51664,7 +51664,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -53148,7 +53148,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -54632,7 +54632,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -56512,7 +56512,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57996,7 +57996,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -59628,7 +59628,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -61112,7 +61112,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -62596,7 +62596,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -64080,7 +64080,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -65712,7 +65712,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -67196,7 +67196,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -68680,7 +68680,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -70164,7 +70164,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71648,7 +71648,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -73132,7 +73132,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -75012,7 +75012,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76496,7 +76496,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -77980,7 +77980,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -79464,7 +79464,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -81096,7 +81096,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -82728,7 +82728,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -84212,7 +84212,7 @@
       </c>
       <c r="AJ445" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK445" t="inlineStr">
@@ -85844,7 +85844,7 @@
       </c>
       <c r="AJ454" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK454" t="inlineStr">
@@ -87328,7 +87328,7 @@
       </c>
       <c r="AJ462" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK462" t="inlineStr">
@@ -88812,7 +88812,7 @@
       </c>
       <c r="AJ470" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK470" t="inlineStr">
@@ -90296,7 +90296,7 @@
       </c>
       <c r="AJ478" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK478" t="inlineStr">

--- a/diseases/d040/2000-2004.xlsx
+++ b/diseases/d040/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18637,7 +18637,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21919,7 +21919,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -23238,7 +23238,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24557,7 +24557,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -25876,7 +25876,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29833,7 +29833,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -31152,7 +31152,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32471,7 +32471,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -33790,7 +33790,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35109,7 +35109,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -36428,7 +36428,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -39792,7 +39792,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -41276,7 +41276,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -42760,7 +42760,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44244,7 +44244,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45728,7 +45728,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -47212,7 +47212,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -48696,7 +48696,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -50180,7 +50180,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51664,7 +51664,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -53148,7 +53148,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -54632,7 +54632,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -56512,7 +56512,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57996,7 +57996,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -59628,7 +59628,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -61112,7 +61112,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -62596,7 +62596,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -64080,7 +64080,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -65712,7 +65712,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -67196,7 +67196,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -68680,7 +68680,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -70164,7 +70164,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71648,7 +71648,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -73132,7 +73132,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -75012,7 +75012,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76496,7 +76496,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -77980,7 +77980,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -79464,7 +79464,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -81096,7 +81096,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -82728,7 +82728,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -84212,7 +84212,7 @@
       </c>
       <c r="AJ445" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK445" t="inlineStr">
@@ -85844,7 +85844,7 @@
       </c>
       <c r="AJ454" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK454" t="inlineStr">
@@ -87328,7 +87328,7 @@
       </c>
       <c r="AJ462" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK462" t="inlineStr">
@@ -88812,7 +88812,7 @@
       </c>
       <c r="AJ470" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK470" t="inlineStr">
@@ -90296,7 +90296,7 @@
       </c>
       <c r="AJ478" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK478" t="inlineStr">

--- a/diseases/d040/2000-2004.xlsx
+++ b/diseases/d040/2000-2004.xlsx
@@ -1161,9 +1161,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1705,9 +1702,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2332,9 +2326,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -3124,9 +3115,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3899,9 +3887,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4691,9 +4676,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5466,9 +5448,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -6258,9 +6237,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -7033,9 +7009,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -7825,9 +7798,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8600,9 +8570,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -9392,9 +9359,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -10167,9 +10131,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -10959,9 +10920,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -11734,9 +11692,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -12526,9 +12481,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -13301,9 +13253,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -14093,9 +14042,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14868,9 +14814,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -15660,9 +15603,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -16435,9 +16375,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -17227,9 +17164,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -18002,9 +17936,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -18794,9 +18725,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -19569,9 +19497,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -20361,9 +20286,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -20905,9 +20827,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -21532,9 +21451,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -22076,9 +21992,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -22851,9 +22764,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -23395,9 +23305,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -24170,9 +24077,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -24714,9 +24618,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -25489,9 +25390,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -26033,9 +25931,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -26808,9 +26703,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -27352,9 +27244,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -28127,9 +28016,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -28671,9 +28557,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -29446,9 +29329,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -29990,9 +29870,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -30765,9 +30642,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -31309,9 +31183,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -32084,9 +31955,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -32628,9 +32496,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -33403,9 +33268,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -33947,9 +33809,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -34722,9 +34581,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -35266,9 +35122,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -36041,9 +35894,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -36585,9 +36435,6 @@
       <c r="O188" t="n">
         <v>1</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -37129,9 +36976,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -37525,9 +37369,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -37673,9 +37514,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -38465,9 +38303,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -39009,9 +38844,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -39157,9 +38989,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -39949,9 +39778,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -40493,9 +40319,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -40641,9 +40464,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -41433,9 +41253,6 @@
       <c r="O214" t="n">
         <v>1</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -41977,9 +41794,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -42125,9 +41939,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -42917,9 +42728,6 @@
       <c r="O222" t="n">
         <v>1</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -43461,9 +43269,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -43609,9 +43414,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -44401,9 +44203,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -44945,9 +44744,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -45093,9 +44889,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -45885,9 +45678,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -46429,9 +46219,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -46577,9 +46364,6 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -47369,9 +47153,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -47913,9 +47694,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -48061,9 +47839,6 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
@@ -48853,9 +48628,6 @@
       <c r="O254" t="n">
         <v>0</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0</v>
       </c>
@@ -49397,9 +49169,6 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
@@ -49545,9 +49314,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -50337,9 +50103,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -50881,9 +50644,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -51029,9 +50789,6 @@
       <c r="O266" t="n">
         <v>1</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -51821,9 +51578,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -52365,9 +52119,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -52513,9 +52264,6 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
@@ -53305,9 +53053,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -53849,9 +53594,6 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
@@ -53997,9 +53739,6 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0</v>
       </c>
@@ -54789,9 +54528,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -55333,9 +55069,6 @@
       <c r="O289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0</v>
       </c>
@@ -55729,9 +55462,6 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -55877,9 +55607,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -56669,9 +56396,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -57213,9 +56937,6 @@
       <c r="O299" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0</v>
       </c>
@@ -57361,9 +57082,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -58153,9 +57871,6 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
@@ -58697,9 +58412,6 @@
       <c r="O307" t="n">
         <v>0</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0</v>
       </c>
@@ -58845,9 +58557,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -59785,9 +59494,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -60329,9 +60035,6 @@
       <c r="O316" t="n">
         <v>0</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0</v>
       </c>
@@ -60477,9 +60180,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -61269,9 +60969,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -61813,9 +61510,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -61961,9 +61655,6 @@
       <c r="O325" t="n">
         <v>0</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0</v>
       </c>
@@ -62753,9 +62444,6 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -63297,9 +62985,6 @@
       <c r="O332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0</v>
       </c>
@@ -63445,9 +63130,6 @@
       <c r="O333" t="n">
         <v>0</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0</v>
       </c>
@@ -64237,9 +63919,6 @@
       <c r="O337" t="n">
         <v>0</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0</v>
       </c>
@@ -64781,9 +64460,6 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0</v>
       </c>
@@ -64929,9 +64605,6 @@
       <c r="O341" t="n">
         <v>0</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0</v>
       </c>
@@ -65869,9 +65542,6 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
@@ -66413,9 +66083,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -66561,9 +66228,6 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0</v>
       </c>
@@ -67353,9 +67017,6 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0</v>
       </c>
@@ -67897,9 +67558,6 @@
       <c r="O357" t="n">
         <v>0</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0</v>
       </c>
@@ -68045,9 +67703,6 @@
       <c r="O358" t="n">
         <v>0</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0</v>
       </c>
@@ -68837,9 +68492,6 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0</v>
       </c>
@@ -69381,9 +69033,6 @@
       <c r="O365" t="n">
         <v>0</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0</v>
       </c>
@@ -69529,9 +69178,6 @@
       <c r="O366" t="n">
         <v>0</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0</v>
       </c>
@@ -70321,9 +69967,6 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0</v>
       </c>
@@ -70865,9 +70508,6 @@
       <c r="O373" t="n">
         <v>0</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0</v>
       </c>
@@ -71013,9 +70653,6 @@
       <c r="O374" t="n">
         <v>1</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -71805,9 +71442,6 @@
       <c r="O378" t="n">
         <v>0</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>0</v>
       </c>
@@ -72349,9 +71983,6 @@
       <c r="O381" t="n">
         <v>0</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0</v>
       </c>
@@ -72497,9 +72128,6 @@
       <c r="O382" t="n">
         <v>0</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0</v>
       </c>
@@ -73289,9 +72917,6 @@
       <c r="O386" t="n">
         <v>0</v>
       </c>
-      <c r="Q386" t="n">
-        <v>0</v>
-      </c>
       <c r="R386" t="n">
         <v>0</v>
       </c>
@@ -73833,9 +73458,6 @@
       <c r="O389" t="n">
         <v>0</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>0</v>
       </c>
@@ -74229,9 +73851,6 @@
       <c r="O391" t="n">
         <v>0</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0</v>
       </c>
@@ -74377,9 +73996,6 @@
       <c r="O392" t="n">
         <v>0</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0</v>
       </c>
@@ -75169,9 +74785,6 @@
       <c r="O396" t="n">
         <v>0</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>0</v>
       </c>
@@ -75713,9 +75326,6 @@
       <c r="O399" t="n">
         <v>0</v>
       </c>
-      <c r="Q399" t="n">
-        <v>0</v>
-      </c>
       <c r="R399" t="n">
         <v>0</v>
       </c>
@@ -75861,9 +75471,6 @@
       <c r="O400" t="n">
         <v>0</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0</v>
       </c>
@@ -76653,9 +76260,6 @@
       <c r="O404" t="n">
         <v>0</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0</v>
       </c>
@@ -77197,9 +76801,6 @@
       <c r="O407" t="n">
         <v>0</v>
       </c>
-      <c r="Q407" t="n">
-        <v>0</v>
-      </c>
       <c r="R407" t="n">
         <v>0</v>
       </c>
@@ -77345,9 +76946,6 @@
       <c r="O408" t="n">
         <v>0</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0</v>
       </c>
@@ -78137,9 +77735,6 @@
       <c r="O412" t="n">
         <v>0</v>
       </c>
-      <c r="Q412" t="n">
-        <v>0</v>
-      </c>
       <c r="R412" t="n">
         <v>0</v>
       </c>
@@ -78681,9 +78276,6 @@
       <c r="O415" t="n">
         <v>0</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0</v>
       </c>
@@ -78829,9 +78421,6 @@
       <c r="O416" t="n">
         <v>0</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0</v>
       </c>
@@ -79621,9 +79210,6 @@
       <c r="O420" t="n">
         <v>0</v>
       </c>
-      <c r="Q420" t="n">
-        <v>0</v>
-      </c>
       <c r="R420" t="n">
         <v>0</v>
       </c>
@@ -80165,9 +79751,6 @@
       <c r="O423" t="n">
         <v>0</v>
       </c>
-      <c r="Q423" t="n">
-        <v>0</v>
-      </c>
       <c r="R423" t="n">
         <v>0</v>
       </c>
@@ -80313,9 +79896,6 @@
       <c r="O424" t="n">
         <v>0</v>
       </c>
-      <c r="Q424" t="n">
-        <v>0</v>
-      </c>
       <c r="R424" t="n">
         <v>0</v>
       </c>
@@ -81253,9 +80833,6 @@
       <c r="O429" t="n">
         <v>0</v>
       </c>
-      <c r="Q429" t="n">
-        <v>0</v>
-      </c>
       <c r="R429" t="n">
         <v>0</v>
       </c>
@@ -81797,9 +81374,6 @@
       <c r="O432" t="n">
         <v>0</v>
       </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
       <c r="R432" t="n">
         <v>0</v>
       </c>
@@ -81945,9 +81519,6 @@
       <c r="O433" t="n">
         <v>0</v>
       </c>
-      <c r="Q433" t="n">
-        <v>0</v>
-      </c>
       <c r="R433" t="n">
         <v>0</v>
       </c>
@@ -82885,9 +82456,6 @@
       <c r="O438" t="n">
         <v>0</v>
       </c>
-      <c r="Q438" t="n">
-        <v>0</v>
-      </c>
       <c r="R438" t="n">
         <v>0</v>
       </c>
@@ -83429,9 +82997,6 @@
       <c r="O441" t="n">
         <v>0</v>
       </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
       <c r="R441" t="n">
         <v>0</v>
       </c>
@@ -83577,9 +83142,6 @@
       <c r="O442" t="n">
         <v>0</v>
       </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
       <c r="R442" t="n">
         <v>0</v>
       </c>
@@ -84369,9 +83931,6 @@
       <c r="O446" t="n">
         <v>0</v>
       </c>
-      <c r="Q446" t="n">
-        <v>0</v>
-      </c>
       <c r="R446" t="n">
         <v>0</v>
       </c>
@@ -84913,9 +84472,6 @@
       <c r="O449" t="n">
         <v>0</v>
       </c>
-      <c r="Q449" t="n">
-        <v>0</v>
-      </c>
       <c r="R449" t="n">
         <v>0</v>
       </c>
@@ -85061,9 +84617,6 @@
       <c r="O450" t="n">
         <v>1</v>
       </c>
-      <c r="Q450" t="n">
-        <v>0</v>
-      </c>
       <c r="R450" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -86001,9 +85554,6 @@
       <c r="O455" t="n">
         <v>0</v>
       </c>
-      <c r="Q455" t="n">
-        <v>0</v>
-      </c>
       <c r="R455" t="n">
         <v>0</v>
       </c>
@@ -86545,9 +86095,6 @@
       <c r="O458" t="n">
         <v>0</v>
       </c>
-      <c r="Q458" t="n">
-        <v>0</v>
-      </c>
       <c r="R458" t="n">
         <v>0</v>
       </c>
@@ -86693,9 +86240,6 @@
       <c r="O459" t="n">
         <v>0</v>
       </c>
-      <c r="Q459" t="n">
-        <v>0</v>
-      </c>
       <c r="R459" t="n">
         <v>0</v>
       </c>
@@ -87485,9 +87029,6 @@
       <c r="O463" t="n">
         <v>0</v>
       </c>
-      <c r="Q463" t="n">
-        <v>0</v>
-      </c>
       <c r="R463" t="n">
         <v>0</v>
       </c>
@@ -88029,9 +87570,6 @@
       <c r="O466" t="n">
         <v>0</v>
       </c>
-      <c r="Q466" t="n">
-        <v>0</v>
-      </c>
       <c r="R466" t="n">
         <v>0</v>
       </c>
@@ -88177,9 +87715,6 @@
       <c r="O467" t="n">
         <v>0</v>
       </c>
-      <c r="Q467" t="n">
-        <v>0</v>
-      </c>
       <c r="R467" t="n">
         <v>0</v>
       </c>
@@ -88969,9 +88504,6 @@
       <c r="O471" t="n">
         <v>0</v>
       </c>
-      <c r="Q471" t="n">
-        <v>0</v>
-      </c>
       <c r="R471" t="n">
         <v>0</v>
       </c>
@@ -89513,9 +89045,6 @@
       <c r="O474" t="n">
         <v>0</v>
       </c>
-      <c r="Q474" t="n">
-        <v>0</v>
-      </c>
       <c r="R474" t="n">
         <v>0</v>
       </c>
@@ -89661,9 +89190,6 @@
       <c r="O475" t="n">
         <v>0</v>
       </c>
-      <c r="Q475" t="n">
-        <v>0</v>
-      </c>
       <c r="R475" t="n">
         <v>0</v>
       </c>
@@ -90453,9 +89979,6 @@
       <c r="O479" t="n">
         <v>0</v>
       </c>
-      <c r="Q479" t="n">
-        <v>0</v>
-      </c>
       <c r="R479" t="n">
         <v>0</v>
       </c>
@@ -90997,9 +90520,6 @@
       <c r="O482" t="n">
         <v>0</v>
       </c>
-      <c r="Q482" t="n">
-        <v>0</v>
-      </c>
       <c r="R482" t="n">
         <v>0</v>
       </c>
@@ -91144,9 +90664,6 @@
       </c>
       <c r="O483" t="n">
         <v>1</v>
-      </c>
-      <c r="Q483" t="n">
-        <v>0</v>
       </c>
       <c r="R483" t="n">
         <v>0.02177822471534499</v>

--- a/diseases/d040/2000-2004.xlsx
+++ b/diseases/d040/2000-2004.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13895,7 +13895,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -23158,7 +23158,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25784,7 +25784,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27097,7 +27097,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29723,7 +29723,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -31036,7 +31036,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32349,7 +32349,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -33662,7 +33662,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34975,7 +34975,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -36288,7 +36288,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38156,7 +38156,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39631,7 +39631,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41106,7 +41106,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -42581,7 +42581,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44056,7 +44056,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45531,7 +45531,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47006,7 +47006,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48481,7 +48481,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -49956,7 +49956,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -51431,7 +51431,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -52906,7 +52906,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -54381,7 +54381,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -56249,7 +56249,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -57724,7 +57724,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -59347,7 +59347,7 @@
       </c>
       <c r="AM312" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN312" t="b">
@@ -60822,7 +60822,7 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN320" t="b">
@@ -62297,7 +62297,7 @@
       </c>
       <c r="AM328" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN328" t="b">
@@ -63772,7 +63772,7 @@
       </c>
       <c r="AM336" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN336" t="b">
@@ -65395,7 +65395,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN345" t="b">
@@ -66870,7 +66870,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN353" t="b">
@@ -68345,7 +68345,7 @@
       </c>
       <c r="AM361" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN361" t="b">
@@ -69820,7 +69820,7 @@
       </c>
       <c r="AM369" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN369" t="b">
@@ -71295,7 +71295,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -72770,7 +72770,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN385" t="b">
@@ -74638,7 +74638,7 @@
       </c>
       <c r="AM395" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN395" t="b">
@@ -76113,7 +76113,7 @@
       </c>
       <c r="AM403" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN403" t="b">
@@ -77588,7 +77588,7 @@
       </c>
       <c r="AM411" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN411" t="b">
@@ -79063,7 +79063,7 @@
       </c>
       <c r="AM419" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN419" t="b">
@@ -80686,7 +80686,7 @@
       </c>
       <c r="AM428" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN428" t="b">
@@ -82309,7 +82309,7 @@
       </c>
       <c r="AM437" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN437" t="b">
@@ -83784,7 +83784,7 @@
       </c>
       <c r="AM445" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN445" t="b">
@@ -85407,7 +85407,7 @@
       </c>
       <c r="AM454" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN454" t="b">
@@ -86882,7 +86882,7 @@
       </c>
       <c r="AM462" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN462" t="b">
@@ -88357,7 +88357,7 @@
       </c>
       <c r="AM470" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN470" t="b">
@@ -89832,7 +89832,7 @@
       </c>
       <c r="AM478" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN478" t="b">

--- a/diseases/d040/2000-2004.xlsx
+++ b/diseases/d040/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -23148,7 +23148,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27087,7 +27087,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -31026,7 +31026,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32339,7 +32339,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34965,7 +34965,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -36278,7 +36278,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38146,7 +38146,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -41096,7 +41096,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -42571,7 +42571,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44046,7 +44046,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45521,7 +45521,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46996,7 +46996,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -48471,7 +48471,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -49946,7 +49946,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51421,7 +51421,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52896,7 +52896,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -54371,7 +54371,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -56239,7 +56239,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57714,7 +57714,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -59337,7 +59337,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -60812,7 +60812,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -62287,7 +62287,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -63762,7 +63762,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -65385,7 +65385,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66860,7 +66860,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -68335,7 +68335,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -69810,7 +69810,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71285,7 +71285,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -72760,7 +72760,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -74628,7 +74628,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76103,7 +76103,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -77578,7 +77578,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -79053,7 +79053,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -80676,7 +80676,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -82299,7 +82299,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -83774,7 +83774,7 @@
       </c>
       <c r="AJ445" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK445" t="inlineStr">
@@ -85397,7 +85397,7 @@
       </c>
       <c r="AJ454" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK454" t="inlineStr">
@@ -86872,7 +86872,7 @@
       </c>
       <c r="AJ462" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK462" t="inlineStr">
@@ -88347,7 +88347,7 @@
       </c>
       <c r="AJ470" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK470" t="inlineStr">
@@ -89822,7 +89822,7 @@
       </c>
       <c r="AJ478" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK478" t="inlineStr">

--- a/diseases/d040/2000-2004.xlsx
+++ b/diseases/d040/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -23148,7 +23148,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27087,7 +27087,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -31026,7 +31026,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32339,7 +32339,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34965,7 +34965,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -36278,7 +36278,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38146,7 +38146,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -41096,7 +41096,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -42571,7 +42571,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44046,7 +44046,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45521,7 +45521,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46996,7 +46996,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -48471,7 +48471,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -49946,7 +49946,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51421,7 +51421,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52896,7 +52896,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -54371,7 +54371,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -56239,7 +56239,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57714,7 +57714,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -59337,7 +59337,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -60812,7 +60812,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -62287,7 +62287,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -63762,7 +63762,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -65385,7 +65385,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66860,7 +66860,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -68335,7 +68335,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -69810,7 +69810,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71285,7 +71285,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -72760,7 +72760,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -74628,7 +74628,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76103,7 +76103,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -77578,7 +77578,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -79053,7 +79053,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -80676,7 +80676,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -82299,7 +82299,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -83774,7 +83774,7 @@
       </c>
       <c r="AJ445" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK445" t="inlineStr">
@@ -85397,7 +85397,7 @@
       </c>
       <c r="AJ454" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK454" t="inlineStr">
@@ -86872,7 +86872,7 @@
       </c>
       <c r="AJ462" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK462" t="inlineStr">
@@ -88347,7 +88347,7 @@
       </c>
       <c r="AJ470" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK470" t="inlineStr">
@@ -89822,7 +89822,7 @@
       </c>
       <c r="AJ478" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK478" t="inlineStr">

--- a/diseases/d040/2000-2004.xlsx
+++ b/diseases/d040/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -23148,7 +23148,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27087,7 +27087,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -31026,7 +31026,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32339,7 +32339,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34965,7 +34965,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -36278,7 +36278,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38146,7 +38146,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -41096,7 +41096,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -42571,7 +42571,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44046,7 +44046,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45521,7 +45521,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46996,7 +46996,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -48471,7 +48471,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -49946,7 +49946,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51421,7 +51421,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52896,7 +52896,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -54371,7 +54371,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -56239,7 +56239,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57714,7 +57714,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -59337,7 +59337,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -60812,7 +60812,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -62287,7 +62287,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -63762,7 +63762,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -65385,7 +65385,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66860,7 +66860,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -68335,7 +68335,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -69810,7 +69810,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -71285,7 +71285,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -72760,7 +72760,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -74628,7 +74628,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -76103,7 +76103,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -77578,7 +77578,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -79053,7 +79053,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -80676,7 +80676,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -82299,7 +82299,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -83774,7 +83774,7 @@
       </c>
       <c r="AJ445" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK445" t="inlineStr">
@@ -85397,7 +85397,7 @@
       </c>
       <c r="AJ454" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK454" t="inlineStr">
@@ -86872,7 +86872,7 @@
       </c>
       <c r="AJ462" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK462" t="inlineStr">
@@ -88347,7 +88347,7 @@
       </c>
       <c r="AJ470" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK470" t="inlineStr">
@@ -89822,7 +89822,7 @@
       </c>
       <c r="AJ478" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK478" t="inlineStr">
